--- a/excel_bai_tap/bai4_danh_sach_hoc_sinh.xlsx
+++ b/excel_bai_tap/bai4_danh_sach_hoc_sinh.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">DANH SÁCH HỌC SINH</t>
   </si>
@@ -65,24 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lân Vân Tài</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yêu cầu:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thay đổi độ rộng các cột cho phù hợp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chọn khối sau đó vào center cross column (tiêu đề dùng Center Across Selection)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Định dạng Font, size cho bảng (Times New Roman, cỡ 12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đổi màu chữ , tô màu nền (tiêu đề đỏ, nền vàng nhạt; tiêu đề lớn xanh đậm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB=(15'+1 tiết*2+KTHK*3)/6</t>
   </si>
 </sst>
 </file>
@@ -93,7 +75,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,14 +121,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -203,7 +177,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -226,14 +200,6 @@
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -488,7 +454,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -705,36 +671,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
